--- a/Datos/indice.xlsx
+++ b/Datos/indice.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\G9-IA\Datos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BOB\Agente IA G9\Datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DFB03A3-60AB-493A-86E8-1A4F12D105E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0760B61E-4E6B-47A3-ABAA-9BC7AF3E0584}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{988E960D-89FA-4CB1-8671-18C4A779E4FE}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{988E960D-89FA-4CB1-8671-18C4A779E4FE}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,34 +36,112 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="33">
   <si>
     <t>Identificador</t>
   </si>
   <si>
-    <t>Nombre PDF</t>
-  </si>
-  <si>
     <t>URL</t>
   </si>
   <si>
     <t>Descripción</t>
   </si>
   <si>
+    <t>2025-01</t>
+  </si>
+  <si>
+    <t>Descripción del Servicio de GLPI</t>
+  </si>
+  <si>
+    <t>Proceso de gestión de un contrato menor TIC</t>
+  </si>
+  <si>
+    <t>Servicio de obtención de certificados RedIRIS</t>
+  </si>
+  <si>
+    <t>https://wiki.stic.ull.es/doku.php?id=sistemas:tcs_rediris:start&amp;s[]=iiaa</t>
+  </si>
+  <si>
+    <t>https://wiki.stic.ull.es/doku.php?id=direccion_proyectos_y_procesos:proceso_contratacion_menor&amp;s[]=iiaa</t>
+  </si>
+  <si>
+    <t>https://wiki.stic.ull.es/doku.php?id=sistemas:servicios:008_glpi:start&amp;s[]=iiaa</t>
+  </si>
+  <si>
     <t>Fecha de publicación</t>
   </si>
   <si>
     <t>Estado</t>
   </si>
   <si>
+    <t>Vigente</t>
+  </si>
+  <si>
     <t>Fecha de fin de vigencia</t>
+  </si>
+  <si>
+    <t>No vigente</t>
+  </si>
+  <si>
+    <t>https://sede.ull.es/ecivilis-site/documentValidation/doc/7063657/U2dFb3oyTVA=</t>
+  </si>
+  <si>
+    <t>Instrucción de vacaciones y permisos PTGAS 2025</t>
+  </si>
+  <si>
+    <t>https://sede.ull.es/ecivilis-site/bulletinBoard/showBulletin/34642:1</t>
+  </si>
+  <si>
+    <t>Instrucción de vacaciones y permisos PTGAS 2024</t>
+  </si>
+  <si>
+    <t>Nombre Archivo</t>
+  </si>
+  <si>
+    <t>083 [TCS Rediris] Servicio de obtención de certificados de duración media (un año) [Wiki del STIC].pdf</t>
+  </si>
+  <si>
+    <t>Instrucción de vacaciones y permisos PTGAS 2024.pdf</t>
+  </si>
+  <si>
+    <t>Instrucción de vacaciones y permisos PTGAS 2025.pdf</t>
+  </si>
+  <si>
+    <t>https://sede.ull.es/ecivilis-site/bulletinBoard/showBulletin/63062:1</t>
+  </si>
+  <si>
+    <t>Instrucción de vacaciones y permisos PTGAS 2026</t>
+  </si>
+  <si>
+    <t>Instrucción de vacaciones y permisos PTGAS 2026.pdf</t>
+  </si>
+  <si>
+    <t>2024-01</t>
+  </si>
+  <si>
+    <t>2026-01</t>
+  </si>
+  <si>
+    <t>082 [Contrato Menor] Proceso de Contratación Menor [Wiki del STIC].pdf</t>
+  </si>
+  <si>
+    <t>2026-02</t>
+  </si>
+  <si>
+    <t>2026-03</t>
+  </si>
+  <si>
+    <t>2026-04</t>
+  </si>
+  <si>
+    <t>008 [GLPI] Gestión de tickets, proyectos y tareas [Wiki del STIC].pdf</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -75,6 +153,14 @@
       <b/>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -104,19 +190,23 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -449,42 +539,187 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C42A3CF1-6928-4532-B57E-9A5D5E143629}">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.140625" customWidth="1"/>
-    <col min="2" max="2" width="30" customWidth="1"/>
-    <col min="3" max="3" width="52.140625" customWidth="1"/>
-    <col min="4" max="4" width="7.85546875" customWidth="1"/>
+    <col min="2" max="2" width="50.42578125" customWidth="1"/>
+    <col min="3" max="3" width="71.140625" customWidth="1"/>
+    <col min="4" max="4" width="56.7109375" customWidth="1"/>
     <col min="5" max="5" width="12.85546875" customWidth="1"/>
     <col min="7" max="7" width="12.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:7" s="3" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="2">
+        <v>45652</v>
+      </c>
+      <c r="F2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="2">
+        <v>55153</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="2" t="s">
+      <c r="B3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="2">
+        <v>45648</v>
+      </c>
+      <c r="F3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="2">
+        <v>45651</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" s="2">
+        <v>46010</v>
+      </c>
+      <c r="F4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="2">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="C5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="2">
+        <v>45627</v>
+      </c>
+      <c r="F5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="2">
+        <v>55153</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="C6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="2">
+        <v>45636</v>
+      </c>
+      <c r="F6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="2">
+        <v>55153</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" t="s">
         <v>6</v>
+      </c>
+      <c r="C7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45667</v>
+      </c>
+      <c r="F7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="2">
+        <v>55153</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D7" r:id="rId1" xr:uid="{983A25D7-357C-49C2-8E05-65402A87B965}"/>
+    <hyperlink ref="D6" r:id="rId2" xr:uid="{366FC9F4-EB30-4C15-B9DA-73978D31980D}"/>
+    <hyperlink ref="D5" r:id="rId3" xr:uid="{9E88B47D-46B8-429A-9D30-3F8B404FDA43}"/>
+    <hyperlink ref="D2" r:id="rId4" xr:uid="{F555A144-362A-4316-8028-24B5B3A99417}"/>
+    <hyperlink ref="D3" r:id="rId5" xr:uid="{DE76D529-9328-485F-9322-A7A392859312}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId6"/>
 </worksheet>
 </file>
--- a/Datos/indice.xlsx
+++ b/Datos/indice.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BOB\Agente IA G9\Datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0760B61E-4E6B-47A3-ABAA-9BC7AF3E0584}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EDD19F5-F04E-4C4E-A34F-77EE65F900FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{988E960D-89FA-4CB1-8671-18C4A779E4FE}"/>
+    <workbookView xWindow="360" yWindow="360" windowWidth="23010" windowHeight="12210" xr2:uid="{988E960D-89FA-4CB1-8671-18C4A779E4FE}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -98,9 +98,6 @@
     <t>Nombre Archivo</t>
   </si>
   <si>
-    <t>083 [TCS Rediris] Servicio de obtención de certificados de duración media (un año) [Wiki del STIC].pdf</t>
-  </si>
-  <si>
     <t>Instrucción de vacaciones y permisos PTGAS 2024.pdf</t>
   </si>
   <si>
@@ -122,9 +119,6 @@
     <t>2026-01</t>
   </si>
   <si>
-    <t>082 [Contrato Menor] Proceso de Contratación Menor [Wiki del STIC].pdf</t>
-  </si>
-  <si>
     <t>2026-02</t>
   </si>
   <si>
@@ -135,6 +129,12 @@
   </si>
   <si>
     <t>008 [GLPI] Gestión de tickets, proyectos y tareas [Wiki del STIC].pdf</t>
+  </si>
+  <si>
+    <t>082 [Contrato Menor] Proceso de Contratación Menor [Wiki del STIC].dokuwiki</t>
+  </si>
+  <si>
+    <t>083 [TCS Rediris] Servicio de obtención de certificados de duración media (un año) [Wiki del STIC].md</t>
   </si>
 </sst>
 </file>
@@ -543,8 +543,8 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.140625" customWidth="1"/>
-    <col min="2" max="2" width="50.42578125" customWidth="1"/>
-    <col min="3" max="3" width="71.140625" customWidth="1"/>
+    <col min="2" max="2" width="45.7109375" customWidth="1"/>
+    <col min="3" max="3" width="97.5703125" customWidth="1"/>
     <col min="4" max="4" width="56.7109375" customWidth="1"/>
     <col min="5" max="5" width="12.85546875" customWidth="1"/>
     <col min="7" max="7" width="12.42578125" customWidth="1"/>
@@ -575,13 +575,13 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s">
         <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>15</v>
@@ -593,7 +593,7 @@
         <v>14</v>
       </c>
       <c r="G2" s="2">
-        <v>55153</v>
+        <v>46022</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -604,7 +604,7 @@
         <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>17</v>
@@ -616,21 +616,21 @@
         <v>14</v>
       </c>
       <c r="G3" s="2">
-        <v>45651</v>
+        <v>45657</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
         <v>24</v>
       </c>
-      <c r="C4" t="s">
-        <v>25</v>
-      </c>
       <c r="D4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E4" s="2">
         <v>46010</v>
@@ -644,13 +644,13 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B5" t="s">
         <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>9</v>
@@ -667,13 +667,13 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B6" t="s">
         <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>8</v>
@@ -690,13 +690,13 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B7" t="s">
         <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>7</v>

--- a/Datos/indice.xlsx
+++ b/Datos/indice.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BOB\Agente IA G9\Datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EDD19F5-F04E-4C4E-A34F-77EE65F900FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46B76032-E74A-4258-8D0B-03A645ECDD28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="360" windowWidth="23010" windowHeight="12210" xr2:uid="{988E960D-89FA-4CB1-8671-18C4A779E4FE}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{988E960D-89FA-4CB1-8671-18C4A779E4FE}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
